--- a/reports/pdf_rolling5_20260807.xlsx
+++ b/reports/pdf_rolling5_20260807.xlsx
@@ -2146,23 +2146,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>44212500</v>
+        <v>31893750</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.20%</t>
+          <t>2.56%→2.67%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>306→321</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2190,23 +2190,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>31893750</v>
+        <v>44212500</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>2.56%→2.67%</t>
+          <t>1.03%→1.20%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>306→321</t>
+          <t>89→104</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260807.xlsx
+++ b/reports/pdf_rolling5_20260807.xlsx
@@ -922,23 +922,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>에스피지  (신규)</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>23</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2508702000</v>
+        <v>2565502800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>4.00%→5.56%</t>
+          <t>0.00%→0.60%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>194→217</t>
+          <t>0→23</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>에스피지  (신규)</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>23</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2565502800</v>
+        <v>2508702000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.60%</t>
+          <t>4.00%→5.56%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>0→23</t>
+          <t>194→217</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2278,23 +2278,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>41670000</v>
+        <v>26055000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.43%→2.59%</t>
+          <t>0.91%→1.00%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -2322,23 +2322,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>54540000</v>
+        <v>41670000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.92%</t>
+          <t>2.43%→2.59%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G55" s="17" t="n"/>
@@ -2350,23 +2350,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>26055000</v>
+        <v>54540000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.91%→1.00%</t>
+          <t>2.72%→2.92%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G56" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260807.xlsx
+++ b/reports/pdf_rolling5_20260807.xlsx
@@ -922,23 +922,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>에스피지  (신규)</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>23</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2565502800</v>
+        <v>2508702000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.60%</t>
+          <t>4.00%→5.56%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>0→23</t>
+          <t>194→217</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>에스피지  (신규)</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>23</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2508702000</v>
+        <v>2565502800</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>4.00%→5.56%</t>
+          <t>0.00%→0.60%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>194→217</t>
+          <t>0→23</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2146,23 +2146,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>31893750</v>
+        <v>44212500</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.56%→2.67%</t>
+          <t>1.03%→1.20%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>306→321</t>
+          <t>89→104</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2190,23 +2190,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>44212500</v>
+        <v>31893750</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.20%</t>
+          <t>2.56%→2.67%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>306→321</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2322,23 +2322,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>41670000</v>
+        <v>54540000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.43%→2.59%</t>
+          <t>2.72%→2.92%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G55" s="17" t="n"/>
@@ -2350,23 +2350,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>54540000</v>
+        <v>41670000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.92%</t>
+          <t>2.43%→2.59%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G56" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260807.xlsx
+++ b/reports/pdf_rolling5_20260807.xlsx
@@ -922,23 +922,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>에스피지  (신규)</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>23</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2508702000</v>
+        <v>2565502800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>4.00%→5.56%</t>
+          <t>0.00%→0.60%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>194→217</t>
+          <t>0→23</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>에스피지  (신규)</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>23</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2565502800</v>
+        <v>2508702000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.60%</t>
+          <t>4.00%→5.56%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>0→23</t>
+          <t>194→217</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2278,23 +2278,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>26055000</v>
+        <v>54540000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>0.91%→1.00%</t>
+          <t>2.72%→2.92%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -2322,23 +2322,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>54540000</v>
+        <v>26055000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.92%</t>
+          <t>0.91%→1.00%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G55" s="17" t="n"/>
